--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131631236</v>
+        <v>131631082</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos6, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>429485</v>
       </c>
       <c r="R2" t="n">
-        <v>6425470</v>
+        <v>6425483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,17 +776,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131631096</v>
+        <v>98012286</v>
       </c>
       <c r="B3" t="n">
-        <v>83273</v>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +820,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos.2, Vg</t>
+          <t>död al, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429602</v>
+        <v>429434</v>
       </c>
       <c r="R3" t="n">
-        <v>6425356</v>
+        <v>6425514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +885,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2021-12-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>algcellerna från bålen avlånga (inga bilder togs)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,47 +908,72 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>blottad död ved # Alnus glutinosa</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131631387</v>
+        <v>131631341</v>
       </c>
       <c r="B4" t="n">
-        <v>85512</v>
+        <v>83343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1971</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +982,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos9, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån pos8, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429517</v>
+        <v>429413</v>
       </c>
       <c r="R4" t="n">
-        <v>6425392</v>
+        <v>6425470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,32 +1064,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131631341</v>
+        <v>131631171</v>
       </c>
       <c r="B5" t="n">
-        <v>83275</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,14 +1098,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos8, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån pos3, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429413</v>
+        <v>429601</v>
       </c>
       <c r="R5" t="n">
-        <v>6425470</v>
+        <v>6425376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,21 +1149,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1124,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131631171</v>
+        <v>131631387</v>
       </c>
       <c r="B6" t="n">
-        <v>83282</v>
+        <v>85590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>1971</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,14 +1199,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos3, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån pos9, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429601</v>
+        <v>429517</v>
       </c>
       <c r="R6" t="n">
-        <v>6425376</v>
+        <v>6425392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1250,21 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131631082</v>
+        <v>131631188</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,50 +1292,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2381</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bandpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Plagiomnium elatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån pos4, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>429485</v>
+        <v>429574</v>
       </c>
       <c r="R7" t="n">
-        <v>6425483</v>
+        <v>6425416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,26 +1375,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1359,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131631214</v>
+        <v>131631320</v>
       </c>
       <c r="B8" t="n">
-        <v>83273</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,37 +1402,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tunarp sumpskogen n om Svartån pos5, Vg</t>
+          <t>Tunarp sumpskogen n om Svartån pos7, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>429549</v>
+        <v>429422</v>
       </c>
       <c r="R8" t="n">
-        <v>6425414</v>
+        <v>6425470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,21 +1477,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1475,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131631294</v>
+        <v>131631236</v>
       </c>
       <c r="B9" t="n">
-        <v>83273</v>
+        <v>79753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,21 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,6 +1579,21 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1573,6 +1606,458 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98012281</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>död al, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>429434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6425514</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>blottad död ved # Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131631096</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83341</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tunarp sumpskogen n om Svartån pos.2, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>429602</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6425356</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131631214</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83341</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tunarp sumpskogen n om Svartån pos5, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>429549</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6425414</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131631294</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83341</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tunarp sumpskogen n om Svartån pos6, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>429485</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6425470</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -945,6 +955,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98012286</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,6 +1076,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631341</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631171</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1278,6 +1303,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631236</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98012281</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1957,6 +2012,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631214</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2058,8 +2118,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131631294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2121,6 +2121,126 @@
       <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131631294</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136439708</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101558</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hammaren, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>429615</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6425458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Östra sidan i bankslänt.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439708</t>
         </is>
       </c>
     </row>
@@ -2138,6 +2258,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101558</v>
+        <v>101571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
